--- a/2018/North1/North1_Members_final.xlsx
+++ b/2018/North1/North1_Members_final.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>تيار قاوم</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب 10452</t>
         </is>
       </c>
     </row>
